--- a/AfterToken/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__enums__.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="2" max="2"/>
@@ -617,304 +617,342 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>cfg.WeaponType</t>
         </is>
       </c>
-      <c r="C4" t="b">
+      <c r="C4" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>武器类型</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="0" t="inlineStr">
         <is>
           <t>Pistol</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="0" t="inlineStr">
         <is>
           <t>手枪</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="0" t="inlineStr">
         <is>
           <t>SMG</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="0" t="inlineStr">
         <is>
           <t>冲锋枪</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="0" t="inlineStr">
         <is>
           <t>Rifle</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="0" t="inlineStr">
         <is>
           <t>步枪</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="0" t="inlineStr">
         <is>
           <t>Sniper</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="0" t="inlineStr">
         <is>
           <t>狙击枪</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="0" t="inlineStr">
         <is>
           <t>Rocket</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="0" t="inlineStr">
         <is>
           <t>火箭筒</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>cfg.BallisticType</t>
         </is>
       </c>
-      <c r="C10" t="b">
+      <c r="C10" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D10" t="b">
+      <c r="D10" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>弹道类型</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="0" t="inlineStr">
         <is>
           <t>Raycast</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="0" t="inlineStr">
         <is>
           <t>射线即时命中</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>Projectile</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="0" t="inlineStr">
         <is>
           <t>投掷物</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>cfg.FireMode</t>
         </is>
       </c>
-      <c r="C13" t="b">
+      <c r="C13" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D13" t="b">
+      <c r="D13" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>开火模式</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="0" t="inlineStr">
         <is>
           <t>单发</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="0" t="inlineStr">
         <is>
           <t>自动</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>cfg.EQuality</t>
         </is>
       </c>
-      <c r="C16" t="b">
+      <c r="C16" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D16" t="b">
+      <c r="D16" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="0" t="inlineStr">
         <is>
           <t>品质</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>白色</t>
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>蓝色</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>Purple</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>绿色</t>
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>紫色</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>蓝色</t>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>黄色</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Purple</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>紫色</t>
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t>红色</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>4</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>橙色</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>cfg.EItemType</t>
+        </is>
+      </c>
+      <c r="C21" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>道具类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>消耗品</t>
         </is>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__enums__.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="2" max="2"/>
@@ -904,55 +904,138 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>cfg.EItemType</t>
         </is>
       </c>
-      <c r="C21" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="C21" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="0" t="inlineStr">
         <is>
           <t>道具类型</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="0" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="J22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="0" t="inlineStr">
         <is>
           <t>材料</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="0" t="inlineStr">
         <is>
           <t>Consumable</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="J23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="0" t="inlineStr">
         <is>
           <t>消耗品</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>cfg.EBuildingType</t>
+        </is>
+      </c>
+      <c r="C24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>建筑类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>工坊</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>农场</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Trade</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>贸易</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Decor</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>装饰</t>
         </is>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__enums__.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="2" max="2"/>
@@ -957,85 +957,138 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>cfg.EBuildingType</t>
         </is>
       </c>
-      <c r="C24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="C24" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="0" t="inlineStr">
         <is>
           <t>建筑类型</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="0" t="inlineStr">
         <is>
           <t>Workshop</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="J25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="0" t="inlineStr">
         <is>
           <t>工坊</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="0" t="inlineStr">
         <is>
           <t>Farm</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="J26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="0" t="inlineStr">
         <is>
           <t>农场</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="0" t="inlineStr">
         <is>
           <t>Trade</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" s="0" t="inlineStr">
         <is>
           <t>贸易</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="0" t="inlineStr">
         <is>
           <t>Decor</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="0" t="inlineStr">
         <is>
           <t>装饰</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>cfg.UnlockContentType</t>
+        </is>
+      </c>
+      <c r="C29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>解锁内容类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>关卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>武器</t>
         </is>
       </c>
     </row>
